--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站关岳路康达路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±8分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>4/20</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±13分钟</t>
+          <t>07:20采样：该车到重点站沪南路御桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>1/20</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±14分钟</t>
+          <t>07:20采样：该车到重点站迎春路长柳路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>3/20</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1332,19 +1332,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站沪南路高科西路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>2/20</t>
         </is>
       </c>
     </row>
@@ -1421,24 +1421,24 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1451,19 +1451,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数160分钟估算，约±5分钟</t>
+          <t>07:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,32 +1507,1444 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>14/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>9/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>177分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>177.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>15/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>163分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数142分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>10/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>5/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>170分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站关岳路康达路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数157分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>170.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>13/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>164分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>4/8</t>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>11/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>12/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>155分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,14 +446,14 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -637,29 +637,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/20</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路御桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路长柳路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 61分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1141,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:46</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1162,7 +1178,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
@@ -1183,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1221,19 +1237,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 56分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1244,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1273,7 +1289,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1294,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1332,19 +1348,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路高科西路 ETA 25分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1359,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1408,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/20</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1451,24 +1467,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金杨路金业路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数137分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1478,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1527,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/20</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1570,24 +1586,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数131分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1597,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1621,7 +1637,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1646,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/20</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1689,24 +1705,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>177分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1716,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,7 +1756,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1765,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/20</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1813,19 +1829,19 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数142分钟，约±7分钟</t>
+          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1835,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1884,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/20</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2016,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2038,24 +2054,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 28分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±14分钟</t>
+          <t>08:21采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2065,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2089,7 +2105,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2114,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/20</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2157,19 +2173,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站关岳路康达路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数157分钟，约±6分钟</t>
+          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2184,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2233,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/20</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2349,7 +2365,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2387,19 +2403,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2414,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2443,7 +2459,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2463,12 +2479,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/20</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2506,24 +2522,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2533,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2557,12 +2573,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2582,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/20</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2625,19 +2641,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2652,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2681,7 +2697,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2701,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/20</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2744,24 +2760,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±10分钟</t>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2771,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2795,12 +2811,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2820,12 +2836,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/20</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2863,24 +2879,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数155分钟估算，约±11分钟</t>
+          <t>08:21采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2919,32 +2935,1198 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>147分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>149分钟</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>08:21采样：该车到重点站康丽路康恩路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>158分钟</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数158分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
+      <c r="AA27" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr">
-        <is>
-          <t>5/20</t>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>142分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,9 +451,9 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 61分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 38分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1046,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1109,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq39，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq49，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1192,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1237,19 +1241,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 56分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 40分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1467,24 +1475,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±7分钟</t>
+          <t>08:41采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1494,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1586,24 +1594,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±12分钟</t>
+          <t>08:41采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1613,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1637,7 +1645,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1662,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1710,19 +1718,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站迎春路长柳路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±11分钟</t>
+          <t>08:41采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1732,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1824,24 +1832,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±10分钟</t>
+          <t>08:41采样：该车到重点站锦绣路罗山路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1851,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2054,24 +2062,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站丁香路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±7分钟</t>
+          <t>08:41采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2081,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2105,7 +2113,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2130,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2173,24 +2181,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>07:31采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数147分钟，约±6分钟</t>
+          <t>08:41采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2200,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2403,19 +2411,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±10分钟</t>
+          <t>08:41采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2430,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2479,12 +2487,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2527,19 +2535,19 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±14分钟</t>
+          <t>08:41采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2606,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2641,24 +2649,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站金杨路金业路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±8分钟</t>
+          <t>08:41采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,7 +2700,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
@@ -2717,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2760,19 +2768,19 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>183分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀康路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+          <t>08:31采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -2879,24 +2887,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±12分钟</t>
+          <t>08:41采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2906,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,7 +2938,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
@@ -2955,7 +2963,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -2998,24 +3006,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±15分钟</t>
+          <t>08:41采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3074,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -3117,24 +3125,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±9分钟</t>
+          <t>08:41采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3144,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3193,12 +3201,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3352,19 +3360,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站康丽路康恩路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数146分钟，约±10分钟</t>
+          <t>08:41采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3374,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3577,19 +3585,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数158分钟估算，约±5分钟</t>
+          <t>08:41采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3604,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3633,7 +3641,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3653,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3834,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3953,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4002,7 +4010,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4025,7 +4033,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4045,7 +4053,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4072,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4086,7 +4094,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -4126,7 +4134,352 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>161.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>14/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -994,27 +994,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 38分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1071,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1109,7 +1113,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq49，推进20站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1241,19 +1245,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:41采样，终点ETA 40分钟</t>
+          <t>SHMAAS末次终点ETA推算：09:12采样，终点ETA 11分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1288,7 +1292,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
@@ -1313,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1361,14 +1365,14 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>同车下一次反向发车09:30，减去该车自身同类时段历史终点停站中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1383,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1412,7 +1416,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1422,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1470,29 +1474,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站康沈路秀沿路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1502,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1526,12 +1530,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1541,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1594,24 +1598,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>09:12采样：该车到重点站五莲路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1621,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1713,24 +1717,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±12分钟</t>
+          <t>09:12采样：该车到重点站康沈路秀沿路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1740,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1764,7 +1768,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
@@ -1779,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1832,19 +1836,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站锦绣路罗山路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>09:12采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1859,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1945,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,10 +1986,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2003,7 +2023,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2062,24 +2082,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
+          <t>08:51采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,7 +2133,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
@@ -2138,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -2181,24 +2201,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±8分钟</t>
+          <t>09:12采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,7 +2228,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2277,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2310,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2323,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2331,10 +2351,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2352,7 +2388,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2411,24 +2447,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±10分钟</t>
+          <t>09:12采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2438,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2487,12 +2523,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2530,24 +2566,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站沪南路高科西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±11分钟</t>
+          <t>09:12采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2557,7 +2593,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,7 +2617,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
@@ -2606,12 +2642,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2649,19 +2685,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站丁香路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±12分钟</t>
+          <t>09:12采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2676,7 +2712,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2761,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2768,24 +2804,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>183分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:31采样：该车到重点站康沈路秀康路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±15分钟</t>
+          <t>09:12采样：该车到重点站迎春路金松路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2795,7 +2831,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,7 +2855,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
@@ -2844,7 +2880,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>183.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2887,24 +2923,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±9分钟</t>
+          <t>09:12采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2914,7 +2950,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,7 +2999,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3006,24 +3042,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站沪南路华夏西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±12分钟</t>
+          <t>09:12采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3033,7 +3069,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,7 +3093,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3082,12 +3118,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -3125,24 +3161,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±8分钟</t>
+          <t>09:12采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3152,7 +3188,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3201,12 +3237,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3303,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3355,24 +3391,24 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±7分钟</t>
+          <t>09:12采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3382,7 +3418,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3467,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3585,24 +3621,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>08:41采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+          <t>09:12采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3612,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3842,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3896,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3970,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3946,7 +3982,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数142分钟估算，约±5分钟</t>
+          <t>09:12采样：该车到重点站莱阳路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3961,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3990,7 +4026,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4015,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4053,24 +4089,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±8分钟</t>
+          <t>09:12采样：该车到重点站康丽路康恩路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4080,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4109,7 +4145,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4129,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4188,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4172,7 +4208,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4199,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,7 +4254,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4248,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4314,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4425,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4474,12 +4510,369 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>15/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -1360,19 +1360,19 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车09:30，减去该车自身同类时段历史终点停站中位数18分钟，约±5分钟</t>
+          <t>同车下一次反向发车09:32，减去该车自身同类时段历史终点停站中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1479,24 +1479,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1603,19 +1603,19 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站五莲路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站康沈路秀沿路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1831,24 +1831,24 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站金杨路金口路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2094,14 +2094,10 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:51采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:41采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2109,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,7 +2134,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2148,22 +2144,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2201,26 +2197,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站金杨路金口路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:54采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2228,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,7 +2249,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2267,22 +2259,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2307,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2343,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,29 +2434,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2474,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,12 +2490,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2513,22 +2505,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2566,26 +2558,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:54采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2593,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2610,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2632,22 +2620,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2685,24 +2673,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±12分钟</t>
+          <t>同车下一次反向发车10:45，减去该车自身同类时段历史终点停站中位数18分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2712,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2729,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2751,22 +2739,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2799,29 +2787,29 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站迎春路金松路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2831,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2843,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2870,22 +2858,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2923,26 +2911,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:11采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2950,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2963,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2989,22 +2973,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3037,29 +3021,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3069,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,12 +3077,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3108,22 +3092,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3161,26 +3145,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3188,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3197,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3237,12 +3217,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3391,19 +3371,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3418,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3467,12 +3447,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -3510,19 +3490,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 28分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
@@ -3533,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3577,13 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3621,24 +3605,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数96分钟，约±6分钟</t>
+          <t>10:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3648,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3851,24 +3835,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+          <t>10:21采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3878,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,12 +3886,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3927,12 +3911,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3970,19 +3954,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站莱阳路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+          <t>10:21采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3997,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4089,24 +4073,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>09:12采样：该车到重点站康丽路康恩路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±7分钟</t>
+          <t>10:21采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4116,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,7 +4149,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4208,19 +4192,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±8分钟</t>
+          <t>10:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4235,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,7 +4248,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4284,12 +4268,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4517,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4553,24 +4537,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±8分钟</t>
+          <t>10:21采样：该车到重点站丁香路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4580,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4578,7 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4609,7 +4593,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4629,12 +4613,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4672,24 +4656,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±8分钟</t>
+          <t>10:21采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4699,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4728,7 +4712,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4748,7 +4732,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4761,24 +4745,24 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4791,34 +4775,34 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>10:21采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4832,47 +4816,1233 @@
       <c r="T37" s="2" t="inlineStr"/>
       <c r="U37" s="2" t="inlineStr">
         <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>17/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站康沈路秀康路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>22/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr">
-        <is>
-          <t>7/27</t>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3140,27 +3140,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 8分钟</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,12 +3196,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3207,22 +3211,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3260,19 +3264,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:31采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
@@ -3283,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,33 +3311,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>24/27</t>
         </is>
       </c>
     </row>
@@ -3366,29 +3374,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站长岛路张杨北路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3398,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,12 +3430,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3437,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>23/27</t>
         </is>
       </c>
     </row>
@@ -3485,27 +3493,31 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:21采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3513,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,12 +3549,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3562,12 +3574,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3610,21 +3622,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:51采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,7 +3669,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3681,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>22/27</t>
         </is>
       </c>
     </row>
@@ -3719,27 +3727,31 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3747,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,33 +3783,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3830,24 +3846,24 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3862,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,12 +3902,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3911,7 +3927,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3949,7 +3965,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3959,19 +3975,19 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3981,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,12 +4021,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4030,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4084,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4085,7 +4101,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -4100,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4124,12 +4140,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4139,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -4192,26 +4208,22 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4219,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4243,12 +4255,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4258,22 +4270,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4313,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程30%处后消失；随后反向物理轨迹由seq50推进至seq55，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4334,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,10 +4354,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq20（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq20映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq50（站名待映射） ETA 13分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4363,7 +4391,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4422,19 +4450,19 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 15分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
@@ -4445,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4469,17 +4497,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4489,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4537,19 +4565,19 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站丁香路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>11:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4564,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4613,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4656,19 +4684,19 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
+          <t>11:21采样：该车到重点站五莲路兰城路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4683,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4722,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4775,24 +4803,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±14分钟</t>
+          <t>11:21采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4802,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,7 +4854,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
@@ -4851,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -4894,24 +4922,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站康沈路秀康路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数103分钟，约±7分钟</t>
+          <t>11:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4921,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,7 +4998,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5013,24 +5041,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+          <t>11:21采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5040,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5089,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5132,22 +5160,26 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>11:21采样：该车到重点站沪南路北中路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5155,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,17 +5211,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5199,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -5247,24 +5279,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±14分钟</t>
+          <t>11:21采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5274,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5323,7 +5355,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5366,24 +5398,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>11:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5393,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5422,7 +5454,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5442,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -5485,19 +5517,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>11:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -5512,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5541,7 +5573,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5561,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5604,19 +5636,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>11:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5631,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5660,7 +5692,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5680,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5767,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±8分钟</t>
+          <t>11:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5750,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5779,7 +5811,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5804,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5842,24 +5874,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+          <t>11:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5869,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5898,7 +5930,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5918,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -5966,19 +5998,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±10分钟</t>
+          <t>11:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5988,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6017,32 +6049,853 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr">
-        <is>
-          <t>139.5</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>6/27</t>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>23/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>24/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,18 +2033,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,22 +2148,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2269,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,18 +2394,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2515,12 +2523,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,22 +2747,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2983,12 +2991,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3102,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3221,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3458,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/27</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3811,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4208,19 +4216,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 28分钟</t>
+          <t>SHMAAS末次终点ETA推算：11:31采样，终点ETA 3分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
@@ -4231,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,7 +4263,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
@@ -4280,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4326,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程30%处后消失；随后反向物理轨迹由seq50推进至seq55，推进5站，达到≥2站确认条件</t>
+          <t>原方向在全程30%处后消失；随后反向物理轨迹由seq50推进至seq61，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4346,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4420,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4445,27 +4453,31 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:21采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4473,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,12 +4509,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4522,12 +4534,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4560,24 +4572,24 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数14分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4592,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,12 +4628,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4641,12 +4653,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4684,26 +4696,22 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站五莲路兰城路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:41采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4711,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,7 +4748,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4760,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4798,29 +4806,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4830,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,12 +4862,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4869,22 +4877,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4917,29 +4925,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4949,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,12 +4981,12 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4998,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5036,29 +5044,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站沪南路北中路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5068,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5092,12 +5100,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5117,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5160,26 +5168,22 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站沪南路北中路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 4分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5187,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,12 +5215,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5236,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -5274,29 +5278,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站锦绣路罗山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5306,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,12 +5334,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5345,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5398,26 +5402,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站迎春路长柳路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5512,29 +5512,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5636,19 +5636,19 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数89分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站周东路川周公路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5755,24 +5755,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±7分钟</t>
+          <t>同车下一次反向发车13:20，减去该车自身同类时段历史终点停站中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5874,19 +5874,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±8分钟</t>
+          <t>12:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5993,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11:21采样：该车到重点站博兴路兰城路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±9分钟</t>
+          <t>12:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6112,24 +6112,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±6分钟</t>
+          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6231,22 +6231,26 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>12:21采样：该车到重点站浦建路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6282,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6298,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>23/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6346,22 +6350,26 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>12:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6369,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6401,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6413,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6461,24 +6469,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+          <t>12:21采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,7 +6525,7 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6537,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6580,24 +6588,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±8分钟</t>
+          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6607,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,7 +6644,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6656,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6707,26 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>12:21采样：该车到重点站莱阳路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6722,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6758,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6766,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>24/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6784,24 +6796,24 @@
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6814,34 +6826,30 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,47 +6863,753 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
         <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W54" s="2" t="inlineStr">
+      <c r="W55" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X54" s="2" t="inlineStr">
+      <c r="X55" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>134.7</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>2/27</t>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,17 +3219,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5636,26 +5636,22 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站周东路川周公路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:31采样，终点ETA 20分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5663,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5692,7 +5688,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5712,7 +5708,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5750,29 +5746,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车13:20，减去该车自身同类时段历史终点停站中位数32分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5782,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,12 +5802,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5831,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5869,29 +5865,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5901,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,12 +5921,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5950,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5988,12 +5984,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -6005,12 +6001,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6020,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,12 +6040,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6059,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6107,29 +6103,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6159,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6178,17 +6174,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6226,29 +6222,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站浦建路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6258,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,12 +6278,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6307,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6350,26 +6346,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6377,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,7 +6398,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6416,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6464,29 +6456,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站白桦路明月路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6496,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6512,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6545,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6588,24 +6580,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±10分钟</t>
+          <t>13:21采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6615,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6707,24 +6699,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站莱阳路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±15分钟</t>
+          <t>13:21采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6734,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,12 +6775,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -6826,22 +6818,26 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>13:21采样：该车到重点站云山路碧云路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6849,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6873,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6893,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6941,24 +6937,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±11分钟</t>
+          <t>13:21采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6968,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,12 +6988,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7017,7 +7013,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7171,24 +7167,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>13:21采样：该车到重点站锦绣路花木路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7198,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7227,7 +7223,7 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7247,12 +7243,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -7290,24 +7286,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+          <t>13:21采样：该车到重点站金杨路云山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7317,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7346,7 +7342,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7366,7 +7362,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7409,24 +7405,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±7分钟</t>
+          <t>13:21采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7436,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7465,7 +7461,7 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7485,12 +7481,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7533,19 +7529,19 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±12分钟</t>
+          <t>13:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7555,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7584,32 +7580,623 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>7/28</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4643,22 +4643,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4877,22 +4877,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -6358,10 +6358,14 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,12 +6397,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6575,29 +6579,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6607,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,12 +6635,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6646,22 +6650,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6694,29 +6698,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站沪南路北中路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,12 +6754,12 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
@@ -6775,7 +6779,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6813,29 +6817,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站云山路碧云路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,12 +6873,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6884,22 +6888,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6932,29 +6936,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站迎春路长柳路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,12 +6992,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7013,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -7046,12 +7050,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,10 +7091,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7108,7 +7120,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7167,24 +7179,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>118分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站锦绣路花木路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±8分钟</t>
+          <t>14:01采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7194,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,7 +7255,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7286,24 +7298,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站金杨路云山路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±10分钟</t>
+          <t>14:01采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7405,19 +7417,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站川周公路康沈路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±9分钟</t>
+          <t>14:01采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7432,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7481,7 +7493,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7524,24 +7536,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数119分钟，约±11分钟</t>
+          <t>14:01采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7551,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7575,7 +7587,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
@@ -7600,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7643,24 +7655,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±12分钟</t>
+          <t>14:01采样：该车到重点站沪南路高科西路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7670,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7699,7 +7711,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7719,12 +7731,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7762,19 +7774,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±5分钟</t>
+          <t>14:01采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7789,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7818,7 +7830,7 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7838,7 +7850,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7881,19 +7893,19 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±13分钟</t>
+          <t>14:01采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -7908,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7937,7 +7949,7 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7957,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8142,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8196,7 +8208,479 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>145.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
           <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,17 +2033,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3577,17 +3577,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,22 +5115,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6703,24 +6703,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6822,12 +6822,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7298,24 +7298,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站浦建路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±7分钟</t>
+          <t>14:21采样：该车到重点站沪南路御桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -7417,24 +7417,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±9分钟</t>
+          <t>14:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7536,24 +7536,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>14:21采样：该车到重点站浦建路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7655,19 +7655,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站沪南路高科西路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±15分钟</t>
+          <t>14:21采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7774,19 +7774,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>14:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7898,19 +7898,19 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:01采样：该车到重点站关岳路康达路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数135分钟，约±13分钟</t>
+          <t>14:21采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8012,19 +8012,19 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+          <t>14:21采样：该车到重点站莱阳路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8131,22 +8131,26 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>14:21采样：该车到重点站川周公路康沈路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8182,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8202,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8323,7 +8327,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8442,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8556,7 +8560,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8626,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8680,7 +8684,245 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>123分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数123分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>121.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>144.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,22 +2263,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,17 +6655,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6941,24 +6941,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7179,24 +7179,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7293,29 +7293,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站沪南路御桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7412,29 +7412,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7531,29 +7531,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站浦建路锦绣路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7650,29 +7650,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7769,29 +7769,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7893,26 +7893,22 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 43分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7920,7 +7916,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7949,7 +7945,7 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7969,12 +7965,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8017,19 +8013,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站莱阳路东陆路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+          <t>15:21采样：该车到重点站沪南路北中路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,12 +8084,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8131,19 +8127,19 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14:21采样：该车到重点站川周公路康沈路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>15:21采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8158,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8203,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8250,22 +8246,26 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>15:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8317,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8365,24 +8365,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±11分钟</t>
+          <t>15:21采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8484,19 +8484,19 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±10分钟</t>
+          <t>15:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.8</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8603,24 +8603,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±10分钟</t>
+          <t>15:21采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,12 +8654,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -8811,24 +8811,24 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8841,34 +8841,30 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8892,37 +8888,501 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>144.7</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>20/28</t>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>152分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数152分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,14 +1307,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,17 +2394,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,22 +3453,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,22 +3925,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,22 +4163,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>143.5</t>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,22 +4758,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,22 +6531,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,22 +7007,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,17 +7483,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7774,24 +7774,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7888,27 +7888,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:21采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7916,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,12 +7944,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7965,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8003,29 +8007,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站沪南路北中路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8035,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,12 +8063,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8084,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8122,29 +8126,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8154,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,12 +8182,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8193,22 +8197,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8241,29 +8245,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8273,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,12 +8301,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8322,12 +8326,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8360,29 +8364,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8392,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,12 +8420,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8441,12 +8445,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8489,21 +8493,17 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 47分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,17 +8535,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8555,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8603,24 +8603,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站川周公路康沈路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±13分钟</t>
+          <t>16:21采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8722,24 +8722,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数123分钟估算，约±5分钟</t>
+          <t>16:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8952,24 +8952,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±13分钟</t>
+          <t>16:21采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9076,19 +9076,19 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数152分钟估算，约±12分钟</t>
+          <t>16:21采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9190,24 +9190,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±8分钟</t>
+          <t>16:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9279,24 +9279,24 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9309,30 +9309,34 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>16:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9346,43 +9350,1102 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr"/>
-      <c r="AC75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>16:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>154分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>147.3</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>135.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>134.2</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2033,22 +2033,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,22 +2148,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2747,22 +2747,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,22 +3219,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3577,17 +3577,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4643,22 +4643,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,22 +6174,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,22 +7245,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,22 +7364,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8131,24 +8131,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8250,24 +8250,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8369,24 +8369,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8483,27 +8483,31 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:21采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8511,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,17 +8539,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8555,17 +8559,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8602,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -8615,12 +8619,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8630,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,12 +8658,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8669,22 +8673,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8717,29 +8721,29 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8749,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,12 +8777,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8788,22 +8792,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8831,12 +8835,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8864,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,10 +8876,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8893,7 +8913,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8947,29 +8967,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8979,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,12 +9023,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9028,12 +9048,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9071,26 +9091,22 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数111分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 52分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9098,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,17 +9138,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9142,12 +9158,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>152.5</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9190,24 +9206,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站康沈路秀康路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±11分钟</t>
+          <t>17:21采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9217,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9241,7 +9257,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
@@ -9266,12 +9282,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9309,24 +9325,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
+          <t>17:21采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9336,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,7 +9401,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9451,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9539,24 +9555,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站浦东大道东波路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±11分钟</t>
+          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9566,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9615,12 +9631,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9658,24 +9674,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>16:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±8分钟</t>
+          <t>17:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9685,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9734,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9854,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9892,24 +9908,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±10分钟</t>
+          <t>17:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9919,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9948,7 +9964,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9968,7 +9984,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10011,24 +10027,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数154分钟估算，约±10分钟</t>
+          <t>17:21采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10038,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10067,7 +10083,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10087,7 +10103,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>149.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10130,24 +10146,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+          <t>17:21采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10157,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10186,7 +10202,7 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10206,12 +10222,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10249,24 +10265,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±15分钟</t>
+          <t>17:21采样：该车到重点站川周公路康沈路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10276,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10305,7 +10321,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10325,12 +10341,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -10368,22 +10384,26 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>17:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10391,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10415,37 +10435,866 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>146.7</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>137.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站莱阳路东陆路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>141.2</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X84" s="2" t="inlineStr">
+      <c r="X88" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y84" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB84" s="2" t="inlineStr">
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:33</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>153分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数153分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>140.5</t>
         </is>
       </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>16/29</t>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,22 +2981,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,22 +3687,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,22 +3925,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,22 +5115,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,22 +5936,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6769,22 +6769,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8726,24 +8726,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -8972,24 +8972,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9038,22 +9038,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9103,10 +9103,14 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 52分钟</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9114,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,37 +9142,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9201,29 +9205,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站云山路碧云路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9233,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,12 +9261,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9282,12 +9286,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>148.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9320,29 +9324,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9352,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9376,12 +9380,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9401,12 +9405,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9521,7 @@
       <c r="AB76" s="2" t="inlineStr"/>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -9555,26 +9559,22 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:21采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9621,22 +9621,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9669,29 +9669,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9908,24 +9908,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±9分钟</t>
+          <t>18:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±6分钟</t>
+          <t>18:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路华夏西路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±12分钟</t>
+          <t>18:21采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10265,24 +10265,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站川周公路康沈路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±13分钟</t>
+          <t>18:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10384,19 +10384,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站莱阳路东陆路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10503,24 +10503,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±7分钟</t>
+          <t>18:21采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>137.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10622,19 +10622,19 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站莱阳路东陆路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±5分钟</t>
+          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10741,19 +10741,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10817,12 +10817,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>143.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10860,22 +10860,26 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>18:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10883,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10907,17 +10911,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10927,17 +10931,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10975,19 +10979,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数153分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11002,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11031,7 +11035,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11051,12 +11055,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11094,24 +11098,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数150分钟估算，约±12分钟</t>
+          <t>18:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11121,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11150,7 +11154,7 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11170,12 +11174,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11213,19 +11217,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数146分钟估算，约±5分钟</t>
+          <t>18:21采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11240,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11269,32 +11273,742 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>131.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>18:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y91" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z91" s="2" t="inlineStr">
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>3/29</t>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>141分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,22 +2263,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2394,22 +2394,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,14 +3453,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>144.7</t>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3692,17 +3692,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4524,22 +4524,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,14 +6293,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>144.7</t>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9162,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9674,24 +9674,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>168分钟</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9740,22 +9740,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>147.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9793,19 +9793,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：18:51采样，终点ETA 15分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr"/>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9840,37 +9840,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9903,12 +9903,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -9920,12 +9920,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9974,14 +9974,14 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>144.7</t>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -10022,24 +10022,24 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10093,22 +10093,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>149.7</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10141,24 +10141,24 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路金口路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>137.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10260,29 +10260,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>134.2</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -10379,29 +10379,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站浦建路锦绣路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,12 +10435,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10503,26 +10503,22 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>165分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10530,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10559,7 +10555,7 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10579,12 +10575,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10622,26 +10618,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数90分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10649,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10673,12 +10665,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10698,12 +10690,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10741,19 +10733,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10768,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10817,12 +10809,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>143.8</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10860,24 +10852,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±12分钟</t>
+          <t>19:21采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10887,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10911,7 +10903,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
@@ -10936,12 +10928,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10979,19 +10971,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数117分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11006,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11055,12 +11047,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11098,24 +11090,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±14分钟</t>
+          <t>19:21采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11125,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,7 +11141,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
@@ -11174,12 +11166,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11217,19 +11209,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数124分钟，约±5分钟</t>
+          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11244,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11293,7 +11285,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11336,24 +11328,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>18:21采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±9分钟</t>
+          <t>19:21采样：该车到重点站沪南路北中路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11363,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11412,12 +11404,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11455,24 +11447,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±10分钟</t>
+          <t>19:21采样：该车到重点站迎春路金松路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11482,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11511,7 +11503,7 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11531,12 +11523,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11574,24 +11566,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:17</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±8分钟</t>
+          <t>19:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11601,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11630,7 +11622,7 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11650,7 +11642,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>157.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11693,22 +11685,26 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>19:21采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11716,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11740,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11760,17 +11756,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11808,19 +11804,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>19:21采样：该车到重点站博兴路兰城路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -11835,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11864,7 +11860,7 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11884,12 +11880,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -11927,19 +11923,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数141分钟估算，约±13分钟</t>
+          <t>19:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11954,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11983,32 +11979,742 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>140.2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>146分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>19:21采样：该车到重点站浦东大道东波路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>147.8</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>26/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y97" s="2" t="inlineStr">
+      <c r="Y99" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z97" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA97" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
         <is>
           <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>144.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>21:48</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>142.8</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>147.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>22:14</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,17 +5936,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,22 +7959,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10384,24 +10384,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10460,12 +10460,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -10515,10 +10515,14 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10526,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,12 +10554,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10580,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10613,27 +10617,31 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：19:21采样，终点ETA 28分钟</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10641,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10665,12 +10673,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10680,22 +10688,22 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10728,29 +10736,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10760,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,12 +10792,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10809,7 +10817,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10847,29 +10855,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±7分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10879,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10903,12 +10911,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10928,12 +10936,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -10966,29 +10974,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10998,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11022,12 +11030,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11047,7 +11055,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11085,29 +11093,29 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11117,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11141,12 +11149,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11166,12 +11174,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11328,19 +11336,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路北中路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站康弘路康丽路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数4分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11355,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11394,17 +11402,17 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11442,29 +11450,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站迎春路金松路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11474,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11498,12 +11506,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11523,12 +11531,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11566,24 +11574,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站金杨路云山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±9分钟</t>
+          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11593,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11642,12 +11650,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11685,24 +11693,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±13分钟</t>
+          <t>20:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11712,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,7 +11744,7 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
@@ -11761,12 +11769,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -11809,14 +11817,14 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站博兴路兰城路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数107分钟，约±5分钟</t>
+          <t>20:21采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -11831,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11880,7 +11888,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11923,24 +11931,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±13分钟</t>
+          <t>20:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11950,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11999,12 +12007,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>140.2</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12042,24 +12050,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>19:21采样：该车到重点站浦东大道东波路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±7分钟</t>
+          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12069,7 +12077,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12118,12 +12126,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>147.8</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -12161,24 +12169,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数137分钟估算，约±9分钟</t>
+          <t>20:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12188,7 +12196,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12217,7 +12225,7 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12237,12 +12245,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12303,7 +12311,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12395,19 +12403,19 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±6分钟</t>
+          <t>20:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -12422,7 +12430,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12451,7 +12459,7 @@
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12471,12 +12479,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12514,24 +12522,24 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>20:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12541,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12570,7 +12578,7 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12590,12 +12598,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>147.2</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -12603,24 +12611,24 @@
       <c r="A103" s="2" t="inlineStr"/>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12633,34 +12641,34 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:14</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>20:21采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12674,47 +12682,404 @@
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>20:21采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W103" s="2" t="inlineStr">
+      <c r="W104" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X103" s="2" t="inlineStr">
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>141.8</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y103" s="2" t="inlineStr">
+      <c r="Y105" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z103" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA103" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB103" s="2" t="inlineStr">
-        <is>
-          <t>141.5</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr">
-        <is>
-          <t>14/30</t>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>139.2</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东35路.xlsx
+++ b/data/export/2026-09-22-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9750,12 +9750,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10822,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11455,24 +11455,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11574,26 +11574,22 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站康沈路秀沿路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:40采样，终点ETA 11分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11601,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11630,7 +11626,7 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11650,12 +11646,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -11688,29 +11684,29 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11720,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11744,12 +11740,12 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11769,12 +11765,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11803,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -11824,12 +11820,12 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路北中路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11839,7 +11835,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11863,12 +11859,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11893,7 +11889,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -11926,29 +11922,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11958,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11982,12 +11978,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -12007,12 +12003,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -12045,29 +12041,29 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12077,7 +12073,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12101,12 +12097,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12126,7 +12122,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12169,19 +12165,19 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>20:40采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -12196,7 +12192,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12245,12 +12241,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12274,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12311,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,10 +12315,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12340,7 +12352,7 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12365,7 +12377,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12408,21 +12420,17 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 28分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12430,7 +12438,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12454,12 +12462,12 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12479,7 +12487,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12517,29 +12525,29 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数79分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -12549,7 +12557,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12573,12 +12581,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12598,12 +12606,12 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -12641,24 +12649,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±9分钟</t>
+          <t>21:21采样：该车到重点站沪南路御桥路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12668,7 +12676,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12717,12 +12725,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12780,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>21:21采样：该车到重点站云山路碧云路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -12787,7 +12795,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12841,7 +12849,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12879,24 +12887,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12906,7 +12914,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12935,7 +12943,7 @@
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
@@ -12955,12 +12963,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12998,24 +13006,24 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±6分钟</t>
+          <t>21:21采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -13025,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13054,7 +13062,7 @@
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
@@ -13074,12 +13082,12 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
